--- a/artfynd/A 8591-2023 artfynd.xlsx
+++ b/artfynd/A 8591-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8591-2023 artfynd.xlsx
+++ b/artfynd/A 8591-2023 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>121344482</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 8591-2023 artfynd.xlsx
+++ b/artfynd/A 8591-2023 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>121344482</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 8591-2023 artfynd.xlsx
+++ b/artfynd/A 8591-2023 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>121344482</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 8591-2023 artfynd.xlsx
+++ b/artfynd/A 8591-2023 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>121344482</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 8591-2023 artfynd.xlsx
+++ b/artfynd/A 8591-2023 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>121344482</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 8591-2023 artfynd.xlsx
+++ b/artfynd/A 8591-2023 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>121344482</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 8591-2023 artfynd.xlsx
+++ b/artfynd/A 8591-2023 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>121344482</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 8591-2023 artfynd.xlsx
+++ b/artfynd/A 8591-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1177,131 +1177,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>121344482</v>
-      </c>
-      <c r="B6" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Långvak, ONO om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>371701</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6616103</v>
-      </c>
-      <c r="S6" t="n">
-        <v>50</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>S-Arv-0606</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>4 dellokaler rapporterade. RT90: 6619929-1326276, 29 ex; 6619933-1326265, 11 ex; 6619960-1326323, 46 ex; 6619967-1326247, 12 ex [oklart om det avser antal skott eller blomstänglar]</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Lisa Ingwall-King</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8591-2023 artfynd.xlsx
+++ b/artfynd/A 8591-2023 artfynd.xlsx
@@ -675,62 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3067148</v>
+        <v>119367740</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fåängen, 825 m NNV om, Vrm</t>
+          <t>Långvak, Långvak, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>371700.7974937824</v>
+        <v>371644</v>
       </c>
       <c r="R2" t="n">
-        <v>6616102.682206692</v>
+        <v>6616090</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-11-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-11-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>mittkoordinat, spridd från 920-247 till 985-465, 490 bladrosetter med 70 fröställningar, några nya blomställningar i knopp</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,40 +766,35 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>äldre blandbarrskog med gran och tall</t>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
+          <t>Lisa Ingwall-King</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Larsson, Elvi Eriksson</t>
+          <t>Lisa Ingwall-King</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3067149</v>
+        <v>3067148</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>490</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -856,14 +831,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fåängen, 800 m N om, Vrm</t>
+          <t>Fåängen, 825 m NNV om, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>371890.5029150221</v>
+        <v>371701</v>
       </c>
       <c r="R3" t="n">
-        <v>6616124.999007856</v>
+        <v>6616103</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -893,24 +868,14 @@
           <t>2012-11-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-11-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>45 bladrosetter med 7 fröställningar, spridd på flera mindre bestånd, även vid 985-465 och 0030-6556</t>
+          <t>mittkoordinat, spridd från 920-247 till 985-465, 490 bladrosetter med 70 fröställningar, några nya blomställningar i knopp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +894,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>granskog med enstaka äldre tallar</t>
+          <t>äldre blandbarrskog med gran och tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -947,15 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119369127</v>
+        <v>3067149</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +942,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,17 +952,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långvak, Långvak, Vrm</t>
+          <t>Fåängen, 800 m N om, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>371734</v>
+        <v>371891</v>
       </c>
       <c r="R4" t="n">
-        <v>6616108</v>
+        <v>6616125</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1026,12 +986,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2012-11-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2012-11-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>45 bladrosetter med 7 fröställningar, spridd på flera mindre bestånd, även vid 985-465 och 0030-6556</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,62 +1008,67 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>granskog med enstaka äldre tallar</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Ingwall-King</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Ingwall-King</t>
+          <t>Per Larsson, Elvi Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119367740</v>
+        <v>119369127</v>
       </c>
       <c r="B5" t="n">
-        <v>91861</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1107,13 +1077,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>371644</v>
+        <v>371734</v>
       </c>
       <c r="R5" t="n">
-        <v>6616090</v>
+        <v>6616108</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1153,16 +1123,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
